--- a/extenbooks/S703_extenbook.xlsx
+++ b/extenbooks/S703_extenbook.xlsx
@@ -1284,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A159"/>
+  <dimension ref="A1:A178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1306,7 +1306,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t># S703 — Figure 7.13 — World Manufacturing ROP and IROP, 1970–1989 (Christodoulopoulos/ISDB)</t>
+          <t># S703 — Figure 7.13 — World Manufacturing WORLDAVG Rate of Profit, 1970–1990 (Christodoulopoulos/ISDB)</t>
         </is>
       </c>
     </row>
@@ -1337,21 +1337,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: data_unavailable</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Authored**: 2026-05-18 · **Machine-digitization revision**: 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
+          <t>**Author**: opus-subagent-ch7-fanout · **2026-07-02 revision**: opus M3 ingestion agent</t>
         </is>
       </c>
     </row>
@@ -1398,22 +1398,30 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>- **Durable digitized source**: `Technical/remediation_campaign/digitization_packet/machine/S703_consensus.csv`</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>- **Overlay evidence**: `Technical/remediation_campaign/digitization_packet/machine/S703_consensus_overlay.png`</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- **Adjudication log**: `Technical/remediation_campaign/digitization_packet/machine/M2_adjudication_log.md`</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>- **Adversarial verification report**: `Technical/remediation_campaign/digitization_packet/machine/M3_verify_report.md`</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1431,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>**S703** is the time-series exhibit Shaikh displays in Fig7.13. Period: 1970–1989.</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1441,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Per the playbook recipe for `content_type = data_unavailable`:</t>
+          <t>## 0. Recovery update (2026-07-02, Decision 0019 — amends 0018) — supersedes the data_unavailable framing below</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1451,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>&gt; "DPR + EPR documenting the chart-only source and why no underlying data exists ... L01 returns SKIPPED ... V03 returns PASS_DATA_UNAVAILABLE ... No chopped CSV."</t>
+          <t>S703 was **RECOVERED** from `data_unavailable` to `book_period_validated` by **machine digitization of the printed figure**. The underlying OECD ISDB / Christodoulopoulos raw data remain unrecoverable (unpublished NSSR working paper, discontinued 1994 ISDB vintage), but the single **WORLDAVG open-circle line** was read directly off Shaikh's printed Figure 7.13 (average panel) at reading fidelity. The status flip and method were authorized under the standing instruction "keep it safe, do what you want with it."</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1461,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 7</t>
+          <t>Fig 7.13 is a **9-series marker-coded "spaghetti" plot** (8 industries + WORLDAVG). We digitized **only the WORLDAVG open-circle (○) line** in the average panel, discriminating it at every year from the MACHEQP open diamond (◇) and the PAPER crossed-square (⊠). `provenance: machine_digitized`. §§1–9 below are updated; the original data_unavailable rationale is retained only as historical context where noted.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1471,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ch7's empirical case for turbulent profit-rate equalization layers four exhibits: US BEA (S705-S710), Greek ESYE (S707/S708), OECD STAN (S711), and the **Christodoulopoulos (1995) world/US ISDB reconstruction** (S703 = Fig7.13). The Christodoulopoulos panel is the longest-running multi-country evidence in the chapter; its **raw data is no longer recoverable** but the published figure remains as historical attestation.</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1481,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
@@ -1483,21 +1491,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher | Status |</t>
+          <t>**S703** is the **WORLDAVG (world manufacturing AVERAGE rate of profit) aggregate line** Shaikh displays in the top/average panel of Fig 7.13. Coverage: 1970–1990, **20 points** (1974 omitted — see §7). It is one line — the world average — isolated from a 9-line figure; the 8 individual world-industry lines are not digitized.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| (none — chart-only) | 1970–1989 | CHRISTODOULOPOULOS_1995_FIG7_13 | **data_unavailable** |</t>
+          <t>Following the 2026-07-02 recovery (§0), this is a **machine-digitized book-period series**, not a `data_unavailable` one: the loader reads the digitized consensus values, the validator round-trips against them, and a chopped CSV plus an extenbook are produced. (The earlier `data_unavailable` handling — loader SKIPPED, validator `PASS_DATA_UNAVAILABLE`, no CSV — no longer applies; it is retained below only as historical context.)</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1511,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The underlying OECD ISDB 1994 vintage was discontinued by OECD; Christodoulopoulos' New School working paper was never published and the raw dataset is not in `SalvagedInputs`. The Phase 4 B5 search documented this explicitly at `SalvagedInputs/book_data/Reconstructed/Christodoulopoulos_1995_data_unavailable.md` (for S703/S704) and `SalvagedInputs/book_data/Reconstructed/Tsoulfidis_Tsaliki_2011_data_unavailable.md` (for S707/S708).</t>
+          <t>## 2. Why it matters in Chapter 7</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1521,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Ch7's empirical case for turbulent profit-rate equalization layers several exhibits: US BEA (S705–S710), the Greek manufacturing pair (S707/S708), OECD STAN (S711), and the **Christodoulopoulos (1995) world ISDB reconstruction** (S703 = Fig 7.13). The Christodoulopoulos panel is the longest-running multi-country evidence in the chapter. Its **raw data are no longer recoverable**, but the printed WORLDAVG line — the world average around which the 8 industry rates cluster — has now been machine-digitized and stands as the recovered aggregate exhibit.</t>
         </is>
       </c>
     </row>
@@ -1527,69 +1531,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>N/A. No data file exists for the loader to ingest. Per the playbook:</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>- `L01` (the loader script) returns `{"status": "SKIPPED", "reason": "data_unavailable"}`.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>- `P02` (the processing script) is not authored.</t>
+          <t>| Subseries | Coverage | Publisher | Status |</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>- `V03` (the validator script) returns `{"status": "PASS_DATA_UNAVAILABLE"}`.</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>- No chopped CSV.</t>
+          <t>| S703-A (WORLDAVG open-circle line, machine-digitized) | 1970–1990 | MACHINE_DIGITIZED_FIG713_WORLDAVG | **book_period_validated** (provenance: machine_digitized) |</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>- Phase 9 visualization uses the book figure image directly.</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>The underlying OECD ISDB 1994 vintage was discontinued by OECD; Christodoulopoulos' New School (NSSR) working paper was never published and the raw dataset is not in `SalvagedInputs`. The Phase 4 B5 search recorded the dead-source finding at `SalvagedInputs/book_data/Reconstructed/Christodoulopoulos_1995_data_unavailable.md`; that note is retained as history and is **superseded** by the 2026-07-02 machine-digitization recovery, which reads Shaikh's printed WORLDAVG line rather than the (still-missing) authors' table.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- **Book period**: 1970–1989</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>- **Extension period**: not applicable (data_unavailable)</t>
+          <t>Machine digitization of the printed WORLDAVG open-circle line in Fig 7.13's average panel (1970–1990, 20 points). The method chain:</t>
         </is>
       </c>
     </row>
@@ -1599,61 +1595,65 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>1. **Dual independent extraction.** Two agents extracted the WORLDAVG line blind to each other — extractor-A geometry-first (marker detection + axis-geometry calibration) and extractor-B sampling-first (curve sampling) — each producing an independent (year, value) table.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2. **Mechanical agreement test.** The two extractions were compared point-by-point; agreement within a threshold (≤2% of the y-range) passed a point RAW.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rate (decimal; would be ROP and IROP world-aggregate).</t>
+          <t>3. **Per-year crop-level marker-identity adjudication.** Every disputed year was re-viewed at high zoom on a cropped image to confirm the WORLDAVG open circle (○) and reject the MACHEQP open diamond (◇) and PAPER crossed-square (⊠).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4. **Adversarial verification.** A fresh agent, working from scratch off the figure and its printed axis glyphs (extractor notes not read), tried and **failed to refute** the curve. Verdict: **CONFIRMED**, no point refuted.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>The consensus values are the durable digitized source (`S703_consensus.csv`). The loader (`L01_S703`) reads that consensus under a returns-precedence guard (see §8) → `data/raw` parquet; `P02_S703` passes it through → `data/processed/S703.parquet`; `V03_S703` round-trips and applies the reference-vertex and plausibility checks (§9). Chopped: `chopped/S703.csv` (20 rows, subseries **S703-A**, long-form). Extenbook: `extenbooks/S703_extenbook.xlsx`.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1. **No byte-exact reproduction possible** from local materials. The published figure stands as the authoritative record.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2. **PDF digitization** (WebPlotDigitizer) is technically possible but is a Phase 9 visualization task, not a Phase 5 data-ingestion task — and would introduce digitization noise that the No-Synthetic rule discourages for primary data.</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>3. **No modern substitute** can splice onto the discontinued ISDB / unredistributed T&amp;T panel without violating the Anti-Degradation rule (industry-mapping drift, country-coverage drift, ESYE→ELSTAT methodology break). Any modern continuation is methodologically separate, not an extension.</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>- **Book period**: 1970–1990 (20 points; **1974 omitted**, §7)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>- **Extension period**: not applicable — the ISDB source is discontinued and not splice-compatible with modern OECD STAN (see `S703_EPR.md`)</t>
         </is>
       </c>
     </row>
@@ -1663,21 +1663,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- **CD legacy ID** (identifier in CD, an earlier predecessor build of this dataset): `S032`</t>
+          <t>**Caption-vs-figure disclosure.** The printed book **caption** reads "1970–1989," but the figure plots a data column hard on the right frame at **1990**, which the adversarial verifier confirmed is the **sharpest circle-vs-diamond discrimination in the whole series**. We honestly include 1990 as a WORLDAVG point; the discrepancy is between the caption text and the plotted figure, and we follow the figure.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig7.13); Appendix 7.1 II / IV (book pp. 856, 859).</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- **B5 provenance document**: see SalvagedInputs/book_data/Reconstructed/ for the relevant `*_data_unavailable.md`.</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1683,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>## Notation (plain-language key)</t>
+          <t>**rate (decimal).** The Fig 7.13 y-axis is decimal, 0–0.45. Values are stored decimal; the chopped `units` column reads `rate_decimal`.</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1693,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -1707,84 +1703,76 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- **S### / -A** — series identifiers in this project (e.g. S703). A trailing letter (e.g. S705-A) marks a *subseries* — one data line within that series.</t>
+          <t>1. **Reading-grade, not table-exact.** The series was recovered by machine digitization of the printed figure, so it is faithful to Shaikh's plotted WORLDAVG line rather than to the authors' exact underlying table (which is not redistributed and remains unrecoverable). The printed figure is the authoritative record.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- **DPR / EPR** — Data Provenance Record (this file) / Extension Provenance Record (its companion).</t>
+          <t>2. **1974 is an honest gap, not filled.** On the steep 1973→1975 descent, no defensible open-circle marker is resolvable — the only resolvable markers in that column are the PAPER crossed-square, the MINERALS filled-square, and a diamond, none of them an open circle. Per the no-interpolation / no-guess rule the 1974 value is **left as a gap** rather than guessed. (The adversarial verifier notes a soft ~0.14 circle is arguably present, but rules the omission a defensible conservative choice.)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension, Phase 9 = visualization.</t>
+          <t>3. **Two knots carry soft marker identity.** The **1973 peak-knot** (circle buried under the PAPER crossed-square) and the **1975 V-trough** (circle ≈ diamond overlap) have soft marker identity; this is already reflected in their low per-point confidences (0.45, 0.47).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+          <t>4. **Transcription confidence MEDIUM-HIGH, ≈ ±0.005 decimal.** Per-point confidence ranges 0.45–0.90 (mean 0.666).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>- **CD / CD2** — earlier predecessor builds of this dataset (CD is older; CD2 is the later predecessor).</t>
+          <t>5. **No modern substitute** can splice onto the discontinued ISDB panel without violating the Anti-Degradation rule (ISIC Rev3→Rev4 industry break, sparse modern capital stock). Any modern continuation is methodologically separate, not an extension.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>- **ROP** — (average) rate of profit.</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>- **ISDB** — International Sectoral Database (OECD).</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>- **STAN** — OECD Structural Analysis database.</t>
+          <t>- **CD legacy ID** (identifier in CD, an earlier predecessor build of this dataset): `S032`</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>- **BEA** — US Bureau of Economic Analysis.</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig 7.13); Appendix 7.1 II / IV (book pp. 856, 859).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>- **ESYE / ELSTAT** — the former Greek national statistical service (ESYE) and its successor (ELSTAT).</t>
+          <t>- **Durable digitized source + evidence**: `Technical/remediation_campaign/digitization_packet/machine/` — `S703_consensus.csv`, `S703_consensus_overlay.png`, `M2_adjudication_log.md`, `M3_verify_report.md`.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>- **T&amp;T** — Tsoulfidis and Tsaliki (2011).</t>
+          <t>- **Precedence rule (keep forever).** If a human-guided digitization is ever filed at `Technical/remediation_campaign/digitization_packet/returns/S703_aggregate_digitized.csv`, it **SUPERSEDES** this machine consensus (provenance rank `human_guided` &gt; `machine_digitized`). The `L01_S703` loader carries a returns-precedence guard that prefers the returns file when present.</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1782,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
@@ -1804,183 +1792,207 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>- **Status**: `PASS_DATA_UNAVAILABLE` (per playbook).</t>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>- No tolerance applies; the validator records that no data exists and that this is the intended state.</t>
+      <c r="A91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S703). A trailing letter (e.g. S703-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>- **WORLDAVG** — the world manufacturing **average** rate of profit: the single aggregate line (world total profit over world total capital) around which the 8 industry lines cluster in Fig 7.13.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>- **Open circle / open diamond / crossed square** — the printed marker glyphs that distinguish the figure's 9 lines: WORLDAVG = open circle (○), MACHEQP = open diamond (◇), PAPER = crossed square (⊠).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record (this file) / Extension Provenance Record (its companion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension, Phase 9 = visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- **CD / CD2** — earlier predecessor builds of this dataset (CD is older; CD2 is the later predecessor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>- **ISDB** — International Sectoral Database (OECD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>- **STAN** — OECD Structural Analysis database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>- **NSSR** — New School for Social Research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>## 9. Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>- **Round-trip**: `V03_S703` reads the digitized consensus back through the loader/processor and confirms the stored values are byte-faithful — **PASS**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>- **Three reference vertices** (Decision 0002; three well-separated, low-ambiguity anchors, decimal): **1970 = 0.1455** (start), **1982 = 0.119** (V-trough), **1990 = 0.1562** (end). Tolerance **±0.005 decimal**, consistent with the MEDIUM-HIGH transcription confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>- **Plausibility**: all values lie within the figure y-axis (0–0.45) and within the WORLDAVG band (0.10–0.20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>- **Anchor suite**: wired to the Decision-0011 anchor suite — **3 GREEN independent anchors**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>- **Gate outcome**: passed the M2 mechanical agreement gate **RAW** (19/20 compared = 95%); the M3 adversarial verifier returned **CONFIRMED**, **no point refuted**. → `publish: true`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4">
         <f>== EPR: S703_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t># S703 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>**Series**: S703 — Figure 7.13 — World Manufacturing ROP and IROP, 1970–1989 (Christodoulopoulos/ISDB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `data_unavailable`</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>**Extension method**: not applicable — see §1</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>**Related**: `S703_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>`content_type = data_unavailable`. There is no byte-exact underlying dataset to extend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>## 2. Why no extension is attempted</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>- The original raw data (Christodoulopoulos 1995 / Tsoulfidis-Tsaliki 2011) is not redistributed in any public form; Shaikh did not redistribute it in his Appendix 7.2 either.</t>
-        </is>
-      </c>
-    </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>- The closest modern source (OECD STAN 2025 for the world / US tracks; ELSTAT post-2010 for the Greek track) has incompatible industry classifications, country coverage, capital-stock coverage, and (for Greece) a 2010 ESYE→ELSTAT methodology break.</t>
+          <t># S703 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>- Any modern panel would be a methodologically separate exhibit, not a faithful extension. Per the Anti-Degradation rule, we do not splice.</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>**Series**: S703 — Figure 7.13 — World Manufacturing WORLDAVG Rate of Profit, 1970–1990 (Christodoulopoulos/ISDB)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `machine_digitized` (book-period only)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>N/A.</t>
+          <t>**Extension method**: not applicable — see §2</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>**extension_status**: `discontinued`</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Authored**: 2026-05-18 · **Machine-digitization revision**: 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch7-fanout · **2026-07-02 revision**: opus M3 ingestion agent</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>**None attempted.** No proxy could meet the Anu No-Proxy bar.</t>
+          <t>**Related**: `S703_DPR.md`</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2002,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2012,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>**None.** No interpolation, no digitization (digitization deferred to Phase 9 visualization, where it is appropriately constrained).</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2022,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>The book-period WORLDAVG line now **exists** — it was machine-digitized off Shaikh's printed Fig 7.13 on 2026-07-02 (see `S703_DPR.md` §0). But there is still **no live-API extension**: the digitized series is **book-period-only** (1970–1990). `extension_status = discontinued`.</t>
         </is>
       </c>
     </row>
@@ -2020,173 +2032,270 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>## 2. Why no extension is attempted</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>| Loader invoked | Returns `{"status": "SKIPPED", "reason": "data_unavailable"}` — by design, not a failure |</t>
+          <t>- The original raw data (OECD ISDB 1994 vintage, via Christodoulopoulos 1995) is **discontinued** and not redistributed in any public form; recovering the book-period values by digitizing the printed figure does **not** make the source live-extendable.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>| Validator invoked | Returns `{"status": "PASS_DATA_UNAVAILABLE"}` |</t>
+          <t>- The closest modern source, **OECD STAN**, is **not splice-compatible**: it carries an **ISIC Rev3 → Rev4 industry break** against ISDB's 8-industry schema, and its **capital-stock coverage is sparse** (many country-industry cells lack gross capital stock — the same obstacle that limited Shaikh's own later OECD work to IROP only).</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>- Any modern panel would therefore be a methodologically separate exhibit, not a faithful extension. Per the Anti-Degradation rule, we do not splice.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CD2 (the predecessor build of this dataset) had no per-series CSV that matches this exhibit's content. The CD2-vs-RSCD comparison is not meaningful here.</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>N/A — no extension. The book-period values are the machine-digitized WORLDAVG line documented in `S703_DPR.md` §4.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>## 8. Recovery paths (out-of-scope for Phase 6)</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Documented in the B5 provenance file at `SalvagedInputs/book_data/Reconstructed/`. The two most plausible long-term recovery paths are:</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1. Author contact (T&amp;T are alive and contactable; Christodoulopoulos last known at NSSR).</t>
+          <t>**None attempted.** No modern proxy could meet the Anu No-Proxy bar across the ISIC Rev3→Rev4 break and the sparse-capital-stock gap.</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2. PDF figure digitization via WebPlotDigitizer (Phase 9 visualization task; would be flagged `provenance: digitized`).</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>## Notation (plain-language key)</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>**None.** No interpolation. The 1974 point is **left as an honest gap**, not filled (see `S703_DPR.md` §7). The book-period digitization itself is a disclosed reading of the printed figure (`provenance: machine_digitized`), not synthetic infill.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>- **S###** — a series identifier in this project (e.g. S703).</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>- **DPR / EPR** — Data Provenance Record / Extension Provenance Record (this file).</t>
+          <t>| Situation | Action |</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>- **Phase N** — Anu Framework pipeline stages: Phase 6 = extension, Phase 9 = visualization.</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>- **CD2** — the predecessor build of this dataset.</t>
+          <t>| Loader invoked | Reads the digitized consensus (returns-precedence guard); emits the 20-point book-period series |</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>- **ROP** — (average) rate of profit.</t>
+          <t>| Extension requested | None — `extension_status = discontinued`; ISDB is not splice-compatible with OECD STAN |</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+          <t>| Validator invoked | Round-trips the digitized values + 3 reference vertices + plausibility band — PASS |</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>- **STAN** — OECD Structural Analysis database.</t>
-        </is>
-      </c>
+      <c r="A156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>- **ESYE / ELSTAT** — the former Greek national statistical service (ESYE) and its successor (ELSTAT).</t>
+          <t>## 7. CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>- **T&amp;T** — Tsoulfidis and Tsaliki (2011).</t>
-        </is>
-      </c>
+      <c r="A158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build of this dataset) had no per-series CSV that matches this exhibit's WORLDAVG content. The CD2-vs-RSCD comparison is not meaningful here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>## 8. Recovery / supersession paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>The book-period recovery is **done** (machine digitization, 2026-07-02). The one remaining path is a **superseding** one, not an extension: if a human-guided digitization is filed at `Technical/remediation_campaign/digitization_packet/returns/S703_aggregate_digitized.csv`, it replaces the machine consensus (`human_guided` &gt; `machine_digitized`); `L01_S703` prefers it automatically. A full data reconstruction from an archived ISDB copy or an OECD-STAN redo would be a *new* exhibit, not an extension of this line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — a series identifier / subseries in this project (e.g. S703, S703-A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>- **WORLDAVG** — the world manufacturing average rate of profit (the single aggregate line in Fig 7.13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record / Extension Provenance Record (this file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 6 = extension, Phase 9 = visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>- **ISDB** — OECD International Sectoral Database (discontinued 1994 vintage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>- **STAN** — OECD Structural Analysis database (successor; ISIC Rev4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>- **ISIC Rev3 / Rev4** — successive revisions of the international industry classification; the Rev3→Rev4 break blocks a clean splice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>- **NSSR** — New School for Social Research.</t>
         </is>
@@ -2207,7 +2316,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
@@ -2270,7 +2379,11 @@
           <t>S703-A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MACHINE_DIGITIZED_FIG713_WORLDAVG</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -2290,10 +2403,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2325,31 +2438,89 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS_DATA_UNAVAILABLE</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>sid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Christodoulopoulos (1995) world ISDB panel not in SalvagedInputs; OECD ISDB 1994 discontinued. PDF figure remains; no chopped CSV.</t>
+          <t>S703</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>n_points</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_range</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[1970, 1990]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>checks</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"round_trip": "PASS", "reference_values": "PASS", "axis_range_0_0.45": "PASS", "occupied_band_0.10_0.20": "PASS"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>machine_digitized (dual independent extraction, crop-level adjudication, adversarial verification 2026-07-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>validation_records</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>["remediation_campaign/digitization_packet/machine/S703_consensus_overlay.png", "remediation_campaign/digitization_packet/machine/M3_verify_report.md", "remediation_campaign/digitization_packet/machine/M2_adjudication_log.md"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-02T06:25:06.070237+00:00</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-11T03:44:27+00:00</t>
         </is>
       </c>
     </row>
@@ -2364,11 +2535,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2391,6 +2562,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CHRISTODOULOPOULOS_1995_FIG7_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>machine_digitized</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "RECOVERED 2026-07-02 by machine digitization (Decision 0019). The WORLDAVG aggregate line was isolated from the 9-series spaghetti by dual independent extraction + crop-level adjudication + adversarial verification (CONFIRMED, no point refuted); 20/21 columns (1974 an honest gap). Values carry per-point transcription confidence. Human returns/ digitization remains a superseding path if ever filed.", "date": "2026-07-02"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S703_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S703_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RECOVERED 2026-07-02 by machine digitization of Fig 7.13 (Decision 0019, amends 0018). Was data_unavailable. WORLDAVG average-panel line only; 1970-1990, 20 points, 1974 omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate (decimal; World manufacturing average rate of profit — Fig 7.13 WORLDAVG line, y-axis 0-0.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
